--- a/Kata Kunci.xlsx
+++ b/Kata Kunci.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Argo\!!2026\AI\Antigravity\berita\Web-Scraping-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Argo\!!2026\Kerja\1. LNPRT\GitHub\lnprt-mencari-berita\lnprt-mencari-berita\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C2440A-4011-4023-A5A2-2CB702E21643}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FB789A-FB7A-4870-BC41-D4DC3972E8AF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7695" activeTab="1" xr2:uid="{A8968677-769D-4485-84B0-F2D4272DC42E}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="89">
   <si>
     <t>Organisasi Kemasyarakatan</t>
   </si>
@@ -287,6 +287,12 @@
   </si>
   <si>
     <t>melemah</t>
+  </si>
+  <si>
+    <t>membaik</t>
+  </si>
+  <si>
+    <t>memburuk</t>
   </si>
 </sst>
 </file>
@@ -859,7 +865,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{733CDB76-AE75-4AF6-86E2-6980EF40DE66}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
@@ -985,6 +991,14 @@
         <v>86</v>
       </c>
     </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
